--- a/Studymaterials/週間学習計画表生徒用_縦型.xlsx
+++ b/Studymaterials/週間学習計画表生徒用_縦型.xlsx
@@ -6,12 +6,12 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="縦型1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="縦型2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="縦型日曜始まり" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="縦型月曜始まり" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'縦型1'!$A$1:$H$58</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'縦型2'!$A$1:$H$58</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'縦型日曜始まり'!$A$1:$H$58</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'縦型月曜始まり'!$A$1:$H$58</definedName>
   </definedNames>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
@@ -68,6 +68,8 @@
     </font>
     <font>
       <name val="ＭＳ Ｐゴシック"/>
+      <charset val="128"/>
+      <family val="3"/>
       <b val="1"/>
       <sz val="14"/>
     </font>
@@ -376,7 +378,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -384,12 +386,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -449,12 +445,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -755,699 +754,699 @@
   <dimension ref="A1:H58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13"/>
   <cols>
-    <col width="8" customWidth="1" style="27" min="1" max="1"/>
-    <col width="12.453125" customWidth="1" style="27" min="2" max="8"/>
+    <col width="8" customWidth="1" style="25" min="1" max="1"/>
+    <col width="12.453125" customWidth="1" style="25" min="2" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="28" t="inlineStr">
+      <c r="A1" s="24" t="inlineStr">
         <is>
           <t>週間学習計画表（縦型）</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="32" customHeight="1" s="27">
-      <c r="A2" s="21" t="inlineStr">
+    <row r="2" ht="32" customHeight="1" s="25">
+      <c r="A2" s="19" t="inlineStr">
         <is>
           <t>週目標</t>
         </is>
       </c>
-      <c r="B2" s="23" t="n"/>
-      <c r="C2" s="24" t="n"/>
-      <c r="D2" s="24" t="n"/>
-      <c r="E2" s="24" t="n"/>
-      <c r="F2" s="24" t="n"/>
-      <c r="G2" s="24" t="n"/>
-      <c r="H2" s="25" t="n"/>
-    </row>
-    <row r="3" ht="18" customHeight="1" s="27">
-      <c r="A3" s="22" t="inlineStr">
+      <c r="B2" s="21" t="n"/>
+      <c r="C2" s="22" t="n"/>
+      <c r="D2" s="22" t="n"/>
+      <c r="E2" s="22" t="n"/>
+      <c r="F2" s="22" t="n"/>
+      <c r="G2" s="22" t="n"/>
+      <c r="H2" s="23" t="n"/>
+    </row>
+    <row r="3" ht="18" customHeight="1" s="25">
+      <c r="A3" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">            日付
 時間</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="26" t="inlineStr">
         <is>
           <t>月　日(日)</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="26" t="inlineStr">
         <is>
           <t>月　日(月)</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="26" t="inlineStr">
         <is>
           <t>月　日(火)</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" s="26" t="inlineStr">
         <is>
           <t>月　日(水)</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" s="26" t="inlineStr">
         <is>
           <t>月　日(木)</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="G3" s="26" t="inlineStr">
         <is>
           <t>月　日(金)</t>
         </is>
       </c>
-      <c r="H3" s="4" t="inlineStr">
+      <c r="H3" s="27" t="inlineStr">
         <is>
           <t>月　日(土)</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="16.5" customHeight="1" s="27">
+    <row r="4" ht="16.5" customHeight="1" s="25">
       <c r="A4" s="1" t="inlineStr">
         <is>
           <t>最優先</t>
         </is>
       </c>
-      <c r="B4" s="5" t="n"/>
-      <c r="C4" s="5" t="n"/>
-      <c r="D4" s="5" t="n"/>
-      <c r="E4" s="5" t="n"/>
-      <c r="F4" s="5" t="n"/>
-      <c r="G4" s="5" t="n"/>
-      <c r="H4" s="6" t="n"/>
+      <c r="B4" s="3" t="n"/>
+      <c r="C4" s="3" t="n"/>
+      <c r="D4" s="3" t="n"/>
+      <c r="E4" s="3" t="n"/>
+      <c r="F4" s="3" t="n"/>
+      <c r="G4" s="3" t="n"/>
+      <c r="H4" s="4" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="n">
+      <c r="A5" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="B5" s="8" t="n"/>
-      <c r="C5" s="8" t="n"/>
-      <c r="D5" s="8" t="n"/>
-      <c r="E5" s="8" t="n"/>
-      <c r="F5" s="8" t="n"/>
-      <c r="G5" s="8" t="n"/>
-      <c r="H5" s="9" t="n"/>
+      <c r="B5" s="6" t="n"/>
+      <c r="C5" s="6" t="n"/>
+      <c r="D5" s="6" t="n"/>
+      <c r="E5" s="6" t="n"/>
+      <c r="F5" s="6" t="n"/>
+      <c r="G5" s="6" t="n"/>
+      <c r="H5" s="7" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="n"/>
-      <c r="B6" s="11" t="n"/>
-      <c r="C6" s="11" t="n"/>
-      <c r="D6" s="11" t="n"/>
-      <c r="E6" s="11" t="n"/>
-      <c r="F6" s="11" t="n"/>
-      <c r="G6" s="11" t="n"/>
-      <c r="H6" s="12" t="n"/>
+      <c r="A6" s="8" t="n"/>
+      <c r="B6" s="9" t="n"/>
+      <c r="C6" s="9" t="n"/>
+      <c r="D6" s="9" t="n"/>
+      <c r="E6" s="9" t="n"/>
+      <c r="F6" s="9" t="n"/>
+      <c r="G6" s="9" t="n"/>
+      <c r="H6" s="10" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="10" t="n">
+      <c r="A7" s="8" t="n">
         <v>0.04166666666666666</v>
       </c>
-      <c r="B7" s="11" t="n"/>
-      <c r="C7" s="11" t="n"/>
-      <c r="D7" s="11" t="n"/>
-      <c r="E7" s="11" t="n"/>
-      <c r="F7" s="11" t="n"/>
-      <c r="G7" s="11" t="n"/>
-      <c r="H7" s="12" t="n"/>
+      <c r="B7" s="9" t="n"/>
+      <c r="C7" s="9" t="n"/>
+      <c r="D7" s="9" t="n"/>
+      <c r="E7" s="9" t="n"/>
+      <c r="F7" s="9" t="n"/>
+      <c r="G7" s="9" t="n"/>
+      <c r="H7" s="10" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="n"/>
-      <c r="B8" s="11" t="n"/>
-      <c r="C8" s="11" t="n"/>
-      <c r="D8" s="11" t="n"/>
-      <c r="E8" s="11" t="n"/>
-      <c r="F8" s="11" t="n"/>
-      <c r="G8" s="11" t="n"/>
-      <c r="H8" s="12" t="n"/>
+      <c r="A8" s="8" t="n"/>
+      <c r="B8" s="9" t="n"/>
+      <c r="C8" s="9" t="n"/>
+      <c r="D8" s="9" t="n"/>
+      <c r="E8" s="9" t="n"/>
+      <c r="F8" s="9" t="n"/>
+      <c r="G8" s="9" t="n"/>
+      <c r="H8" s="10" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="10" t="n">
+      <c r="A9" s="8" t="n">
         <v>0.08333333333333333</v>
       </c>
-      <c r="B9" s="11" t="n"/>
-      <c r="C9" s="11" t="n"/>
-      <c r="D9" s="11" t="n"/>
-      <c r="E9" s="11" t="n"/>
-      <c r="F9" s="11" t="n"/>
-      <c r="G9" s="11" t="n"/>
-      <c r="H9" s="12" t="n"/>
+      <c r="B9" s="9" t="n"/>
+      <c r="C9" s="9" t="n"/>
+      <c r="D9" s="9" t="n"/>
+      <c r="E9" s="9" t="n"/>
+      <c r="F9" s="9" t="n"/>
+      <c r="G9" s="9" t="n"/>
+      <c r="H9" s="10" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="10" t="n"/>
-      <c r="B10" s="11" t="n"/>
-      <c r="C10" s="11" t="n"/>
-      <c r="D10" s="11" t="n"/>
-      <c r="E10" s="11" t="n"/>
-      <c r="F10" s="11" t="n"/>
-      <c r="G10" s="11" t="n"/>
-      <c r="H10" s="12" t="n"/>
+      <c r="A10" s="8" t="n"/>
+      <c r="B10" s="9" t="n"/>
+      <c r="C10" s="9" t="n"/>
+      <c r="D10" s="9" t="n"/>
+      <c r="E10" s="9" t="n"/>
+      <c r="F10" s="9" t="n"/>
+      <c r="G10" s="9" t="n"/>
+      <c r="H10" s="10" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="10" t="n">
+      <c r="A11" s="8" t="n">
         <v>0.125</v>
       </c>
-      <c r="B11" s="11" t="n"/>
-      <c r="C11" s="11" t="n"/>
-      <c r="D11" s="11" t="n"/>
-      <c r="E11" s="11" t="n"/>
-      <c r="F11" s="11" t="n"/>
-      <c r="G11" s="11" t="n"/>
-      <c r="H11" s="12" t="n"/>
+      <c r="B11" s="9" t="n"/>
+      <c r="C11" s="9" t="n"/>
+      <c r="D11" s="9" t="n"/>
+      <c r="E11" s="9" t="n"/>
+      <c r="F11" s="9" t="n"/>
+      <c r="G11" s="9" t="n"/>
+      <c r="H11" s="10" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="10" t="n"/>
-      <c r="B12" s="11" t="n"/>
-      <c r="C12" s="11" t="n"/>
-      <c r="D12" s="11" t="n"/>
-      <c r="E12" s="11" t="n"/>
-      <c r="F12" s="11" t="n"/>
-      <c r="G12" s="11" t="n"/>
-      <c r="H12" s="12" t="n"/>
+      <c r="A12" s="8" t="n"/>
+      <c r="B12" s="9" t="n"/>
+      <c r="C12" s="9" t="n"/>
+      <c r="D12" s="9" t="n"/>
+      <c r="E12" s="9" t="n"/>
+      <c r="F12" s="9" t="n"/>
+      <c r="G12" s="9" t="n"/>
+      <c r="H12" s="10" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="10" t="n">
+      <c r="A13" s="8" t="n">
         <v>0.1666666666666667</v>
       </c>
-      <c r="B13" s="11" t="n"/>
-      <c r="C13" s="11" t="n"/>
-      <c r="D13" s="11" t="n"/>
-      <c r="E13" s="11" t="n"/>
-      <c r="F13" s="11" t="n"/>
-      <c r="G13" s="11" t="n"/>
-      <c r="H13" s="12" t="n"/>
+      <c r="B13" s="9" t="n"/>
+      <c r="C13" s="9" t="n"/>
+      <c r="D13" s="9" t="n"/>
+      <c r="E13" s="9" t="n"/>
+      <c r="F13" s="9" t="n"/>
+      <c r="G13" s="9" t="n"/>
+      <c r="H13" s="10" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="10" t="n"/>
-      <c r="B14" s="11" t="n"/>
-      <c r="C14" s="11" t="n"/>
-      <c r="D14" s="11" t="n"/>
-      <c r="E14" s="11" t="n"/>
-      <c r="F14" s="11" t="n"/>
-      <c r="G14" s="11" t="n"/>
-      <c r="H14" s="12" t="n"/>
+      <c r="A14" s="8" t="n"/>
+      <c r="B14" s="9" t="n"/>
+      <c r="C14" s="9" t="n"/>
+      <c r="D14" s="9" t="n"/>
+      <c r="E14" s="9" t="n"/>
+      <c r="F14" s="9" t="n"/>
+      <c r="G14" s="9" t="n"/>
+      <c r="H14" s="10" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="10" t="n">
+      <c r="A15" s="8" t="n">
         <v>0.2083333333333333</v>
       </c>
-      <c r="B15" s="11" t="n"/>
-      <c r="C15" s="11" t="n"/>
-      <c r="D15" s="11" t="n"/>
-      <c r="E15" s="11" t="n"/>
-      <c r="F15" s="11" t="n"/>
-      <c r="G15" s="11" t="n"/>
-      <c r="H15" s="12" t="n"/>
+      <c r="B15" s="9" t="n"/>
+      <c r="C15" s="9" t="n"/>
+      <c r="D15" s="9" t="n"/>
+      <c r="E15" s="9" t="n"/>
+      <c r="F15" s="9" t="n"/>
+      <c r="G15" s="9" t="n"/>
+      <c r="H15" s="10" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="10" t="n"/>
-      <c r="B16" s="11" t="n"/>
-      <c r="C16" s="11" t="n"/>
-      <c r="D16" s="11" t="n"/>
-      <c r="E16" s="11" t="n"/>
-      <c r="F16" s="11" t="n"/>
-      <c r="G16" s="11" t="n"/>
-      <c r="H16" s="12" t="n"/>
+      <c r="A16" s="8" t="n"/>
+      <c r="B16" s="9" t="n"/>
+      <c r="C16" s="9" t="n"/>
+      <c r="D16" s="9" t="n"/>
+      <c r="E16" s="9" t="n"/>
+      <c r="F16" s="9" t="n"/>
+      <c r="G16" s="9" t="n"/>
+      <c r="H16" s="10" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="10" t="n">
+      <c r="A17" s="8" t="n">
         <v>0.25</v>
       </c>
-      <c r="B17" s="11" t="n"/>
-      <c r="C17" s="11" t="n"/>
-      <c r="D17" s="11" t="n"/>
-      <c r="E17" s="11" t="n"/>
-      <c r="F17" s="11" t="n"/>
-      <c r="G17" s="11" t="n"/>
-      <c r="H17" s="12" t="n"/>
+      <c r="B17" s="9" t="n"/>
+      <c r="C17" s="9" t="n"/>
+      <c r="D17" s="9" t="n"/>
+      <c r="E17" s="9" t="n"/>
+      <c r="F17" s="9" t="n"/>
+      <c r="G17" s="9" t="n"/>
+      <c r="H17" s="10" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="10" t="n"/>
-      <c r="B18" s="11" t="n"/>
-      <c r="C18" s="11" t="n"/>
-      <c r="D18" s="11" t="n"/>
-      <c r="E18" s="11" t="n"/>
-      <c r="F18" s="11" t="n"/>
-      <c r="G18" s="11" t="n"/>
-      <c r="H18" s="12" t="n"/>
+      <c r="A18" s="8" t="n"/>
+      <c r="B18" s="9" t="n"/>
+      <c r="C18" s="9" t="n"/>
+      <c r="D18" s="9" t="n"/>
+      <c r="E18" s="9" t="n"/>
+      <c r="F18" s="9" t="n"/>
+      <c r="G18" s="9" t="n"/>
+      <c r="H18" s="10" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="10" t="n">
+      <c r="A19" s="8" t="n">
         <v>0.2916666666666667</v>
       </c>
-      <c r="B19" s="11" t="n"/>
-      <c r="C19" s="11" t="n"/>
-      <c r="D19" s="11" t="n"/>
-      <c r="E19" s="11" t="n"/>
-      <c r="F19" s="11" t="n"/>
-      <c r="G19" s="11" t="n"/>
-      <c r="H19" s="12" t="n"/>
+      <c r="B19" s="9" t="n"/>
+      <c r="C19" s="9" t="n"/>
+      <c r="D19" s="9" t="n"/>
+      <c r="E19" s="9" t="n"/>
+      <c r="F19" s="9" t="n"/>
+      <c r="G19" s="9" t="n"/>
+      <c r="H19" s="10" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="10" t="n"/>
-      <c r="B20" s="11" t="n"/>
-      <c r="C20" s="11" t="n"/>
-      <c r="D20" s="11" t="n"/>
-      <c r="E20" s="11" t="n"/>
-      <c r="F20" s="11" t="n"/>
-      <c r="G20" s="11" t="n"/>
-      <c r="H20" s="12" t="n"/>
+      <c r="A20" s="8" t="n"/>
+      <c r="B20" s="9" t="n"/>
+      <c r="C20" s="9" t="n"/>
+      <c r="D20" s="9" t="n"/>
+      <c r="E20" s="9" t="n"/>
+      <c r="F20" s="9" t="n"/>
+      <c r="G20" s="9" t="n"/>
+      <c r="H20" s="10" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="10" t="n">
+      <c r="A21" s="8" t="n">
         <v>0.3333333333333333</v>
       </c>
-      <c r="B21" s="11" t="n"/>
-      <c r="C21" s="11" t="n"/>
-      <c r="D21" s="11" t="n"/>
-      <c r="E21" s="11" t="n"/>
-      <c r="F21" s="11" t="n"/>
-      <c r="G21" s="11" t="n"/>
-      <c r="H21" s="12" t="n"/>
+      <c r="B21" s="9" t="n"/>
+      <c r="C21" s="9" t="n"/>
+      <c r="D21" s="9" t="n"/>
+      <c r="E21" s="9" t="n"/>
+      <c r="F21" s="9" t="n"/>
+      <c r="G21" s="9" t="n"/>
+      <c r="H21" s="10" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="10" t="n"/>
-      <c r="B22" s="11" t="n"/>
-      <c r="C22" s="11" t="n"/>
-      <c r="D22" s="11" t="n"/>
-      <c r="E22" s="11" t="n"/>
-      <c r="F22" s="11" t="n"/>
-      <c r="G22" s="11" t="n"/>
-      <c r="H22" s="12" t="n"/>
+      <c r="A22" s="8" t="n"/>
+      <c r="B22" s="9" t="n"/>
+      <c r="C22" s="9" t="n"/>
+      <c r="D22" s="9" t="n"/>
+      <c r="E22" s="9" t="n"/>
+      <c r="F22" s="9" t="n"/>
+      <c r="G22" s="9" t="n"/>
+      <c r="H22" s="10" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="10" t="n">
+      <c r="A23" s="8" t="n">
         <v>0.375</v>
       </c>
-      <c r="B23" s="11" t="n"/>
-      <c r="C23" s="11" t="n"/>
-      <c r="D23" s="11" t="n"/>
-      <c r="E23" s="11" t="n"/>
-      <c r="F23" s="11" t="n"/>
-      <c r="G23" s="11" t="n"/>
-      <c r="H23" s="12" t="n"/>
+      <c r="B23" s="9" t="n"/>
+      <c r="C23" s="9" t="n"/>
+      <c r="D23" s="9" t="n"/>
+      <c r="E23" s="9" t="n"/>
+      <c r="F23" s="9" t="n"/>
+      <c r="G23" s="9" t="n"/>
+      <c r="H23" s="10" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="10" t="n"/>
-      <c r="B24" s="11" t="n"/>
-      <c r="C24" s="11" t="n"/>
-      <c r="D24" s="11" t="n"/>
-      <c r="E24" s="11" t="n"/>
-      <c r="F24" s="11" t="n"/>
-      <c r="G24" s="11" t="n"/>
-      <c r="H24" s="12" t="n"/>
+      <c r="A24" s="8" t="n"/>
+      <c r="B24" s="9" t="n"/>
+      <c r="C24" s="9" t="n"/>
+      <c r="D24" s="9" t="n"/>
+      <c r="E24" s="9" t="n"/>
+      <c r="F24" s="9" t="n"/>
+      <c r="G24" s="9" t="n"/>
+      <c r="H24" s="10" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="10" t="n">
+      <c r="A25" s="8" t="n">
         <v>0.4166666666666667</v>
       </c>
-      <c r="B25" s="11" t="n"/>
-      <c r="C25" s="11" t="n"/>
-      <c r="D25" s="11" t="n"/>
-      <c r="E25" s="11" t="n"/>
-      <c r="F25" s="11" t="n"/>
-      <c r="G25" s="11" t="n"/>
-      <c r="H25" s="12" t="n"/>
+      <c r="B25" s="9" t="n"/>
+      <c r="C25" s="9" t="n"/>
+      <c r="D25" s="9" t="n"/>
+      <c r="E25" s="9" t="n"/>
+      <c r="F25" s="9" t="n"/>
+      <c r="G25" s="9" t="n"/>
+      <c r="H25" s="10" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="10" t="n"/>
-      <c r="B26" s="11" t="n"/>
-      <c r="C26" s="11" t="n"/>
-      <c r="D26" s="11" t="n"/>
-      <c r="E26" s="11" t="n"/>
-      <c r="F26" s="11" t="n"/>
-      <c r="G26" s="11" t="n"/>
-      <c r="H26" s="12" t="n"/>
+      <c r="A26" s="8" t="n"/>
+      <c r="B26" s="9" t="n"/>
+      <c r="C26" s="9" t="n"/>
+      <c r="D26" s="9" t="n"/>
+      <c r="E26" s="9" t="n"/>
+      <c r="F26" s="9" t="n"/>
+      <c r="G26" s="9" t="n"/>
+      <c r="H26" s="10" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="10" t="n">
+      <c r="A27" s="8" t="n">
         <v>0.4583333333333333</v>
       </c>
-      <c r="B27" s="11" t="n"/>
-      <c r="C27" s="11" t="n"/>
-      <c r="D27" s="11" t="n"/>
-      <c r="E27" s="11" t="n"/>
-      <c r="F27" s="11" t="n"/>
-      <c r="G27" s="11" t="n"/>
-      <c r="H27" s="12" t="n"/>
+      <c r="B27" s="9" t="n"/>
+      <c r="C27" s="9" t="n"/>
+      <c r="D27" s="9" t="n"/>
+      <c r="E27" s="9" t="n"/>
+      <c r="F27" s="9" t="n"/>
+      <c r="G27" s="9" t="n"/>
+      <c r="H27" s="10" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="10" t="n"/>
-      <c r="B28" s="11" t="n"/>
-      <c r="C28" s="11" t="n"/>
-      <c r="D28" s="11" t="n"/>
-      <c r="E28" s="11" t="n"/>
-      <c r="F28" s="11" t="n"/>
-      <c r="G28" s="11" t="n"/>
-      <c r="H28" s="12" t="n"/>
+      <c r="A28" s="8" t="n"/>
+      <c r="B28" s="9" t="n"/>
+      <c r="C28" s="9" t="n"/>
+      <c r="D28" s="9" t="n"/>
+      <c r="E28" s="9" t="n"/>
+      <c r="F28" s="9" t="n"/>
+      <c r="G28" s="9" t="n"/>
+      <c r="H28" s="10" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="10" t="n">
+      <c r="A29" s="8" t="n">
         <v>0.5</v>
       </c>
-      <c r="B29" s="11" t="n"/>
-      <c r="C29" s="11" t="n"/>
-      <c r="D29" s="11" t="n"/>
-      <c r="E29" s="11" t="n"/>
-      <c r="F29" s="11" t="n"/>
-      <c r="G29" s="11" t="n"/>
-      <c r="H29" s="12" t="n"/>
+      <c r="B29" s="9" t="n"/>
+      <c r="C29" s="9" t="n"/>
+      <c r="D29" s="9" t="n"/>
+      <c r="E29" s="9" t="n"/>
+      <c r="F29" s="9" t="n"/>
+      <c r="G29" s="9" t="n"/>
+      <c r="H29" s="10" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="10" t="n"/>
-      <c r="B30" s="11" t="n"/>
-      <c r="C30" s="11" t="n"/>
-      <c r="D30" s="11" t="n"/>
-      <c r="E30" s="11" t="n"/>
-      <c r="F30" s="11" t="n"/>
-      <c r="G30" s="11" t="n"/>
-      <c r="H30" s="12" t="n"/>
+      <c r="A30" s="8" t="n"/>
+      <c r="B30" s="9" t="n"/>
+      <c r="C30" s="9" t="n"/>
+      <c r="D30" s="9" t="n"/>
+      <c r="E30" s="9" t="n"/>
+      <c r="F30" s="9" t="n"/>
+      <c r="G30" s="9" t="n"/>
+      <c r="H30" s="10" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="10" t="n">
+      <c r="A31" s="8" t="n">
         <v>0.5416666666666666</v>
       </c>
-      <c r="B31" s="11" t="n"/>
-      <c r="C31" s="11" t="n"/>
-      <c r="D31" s="11" t="n"/>
-      <c r="E31" s="11" t="n"/>
-      <c r="F31" s="11" t="n"/>
-      <c r="G31" s="11" t="n"/>
-      <c r="H31" s="12" t="n"/>
+      <c r="B31" s="9" t="n"/>
+      <c r="C31" s="9" t="n"/>
+      <c r="D31" s="9" t="n"/>
+      <c r="E31" s="9" t="n"/>
+      <c r="F31" s="9" t="n"/>
+      <c r="G31" s="9" t="n"/>
+      <c r="H31" s="10" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="10" t="n"/>
-      <c r="B32" s="11" t="n"/>
-      <c r="C32" s="11" t="n"/>
-      <c r="D32" s="11" t="n"/>
-      <c r="E32" s="11" t="n"/>
-      <c r="F32" s="11" t="n"/>
-      <c r="G32" s="11" t="n"/>
-      <c r="H32" s="12" t="n"/>
+      <c r="A32" s="8" t="n"/>
+      <c r="B32" s="9" t="n"/>
+      <c r="C32" s="9" t="n"/>
+      <c r="D32" s="9" t="n"/>
+      <c r="E32" s="9" t="n"/>
+      <c r="F32" s="9" t="n"/>
+      <c r="G32" s="9" t="n"/>
+      <c r="H32" s="10" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="10" t="n">
+      <c r="A33" s="8" t="n">
         <v>0.5833333333333334</v>
       </c>
-      <c r="B33" s="11" t="n"/>
-      <c r="C33" s="11" t="n"/>
-      <c r="D33" s="11" t="n"/>
-      <c r="E33" s="11" t="n"/>
-      <c r="F33" s="11" t="n"/>
-      <c r="G33" s="11" t="n"/>
-      <c r="H33" s="12" t="n"/>
+      <c r="B33" s="9" t="n"/>
+      <c r="C33" s="9" t="n"/>
+      <c r="D33" s="9" t="n"/>
+      <c r="E33" s="9" t="n"/>
+      <c r="F33" s="9" t="n"/>
+      <c r="G33" s="9" t="n"/>
+      <c r="H33" s="10" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="10" t="n"/>
-      <c r="B34" s="11" t="n"/>
-      <c r="C34" s="11" t="n"/>
-      <c r="D34" s="11" t="n"/>
-      <c r="E34" s="11" t="n"/>
-      <c r="F34" s="11" t="n"/>
-      <c r="G34" s="11" t="n"/>
-      <c r="H34" s="12" t="n"/>
+      <c r="A34" s="8" t="n"/>
+      <c r="B34" s="9" t="n"/>
+      <c r="C34" s="9" t="n"/>
+      <c r="D34" s="9" t="n"/>
+      <c r="E34" s="9" t="n"/>
+      <c r="F34" s="9" t="n"/>
+      <c r="G34" s="9" t="n"/>
+      <c r="H34" s="10" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="10" t="n">
+      <c r="A35" s="8" t="n">
         <v>0.625</v>
       </c>
-      <c r="B35" s="11" t="n"/>
-      <c r="C35" s="11" t="n"/>
-      <c r="D35" s="11" t="n"/>
-      <c r="E35" s="11" t="n"/>
-      <c r="F35" s="11" t="n"/>
-      <c r="G35" s="11" t="n"/>
-      <c r="H35" s="12" t="n"/>
+      <c r="B35" s="9" t="n"/>
+      <c r="C35" s="9" t="n"/>
+      <c r="D35" s="9" t="n"/>
+      <c r="E35" s="9" t="n"/>
+      <c r="F35" s="9" t="n"/>
+      <c r="G35" s="9" t="n"/>
+      <c r="H35" s="10" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="10" t="n"/>
-      <c r="B36" s="11" t="n"/>
-      <c r="C36" s="11" t="n"/>
-      <c r="D36" s="11" t="n"/>
-      <c r="E36" s="11" t="n"/>
-      <c r="F36" s="11" t="n"/>
-      <c r="G36" s="11" t="n"/>
-      <c r="H36" s="12" t="n"/>
+      <c r="A36" s="8" t="n"/>
+      <c r="B36" s="9" t="n"/>
+      <c r="C36" s="9" t="n"/>
+      <c r="D36" s="9" t="n"/>
+      <c r="E36" s="9" t="n"/>
+      <c r="F36" s="9" t="n"/>
+      <c r="G36" s="9" t="n"/>
+      <c r="H36" s="10" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="10" t="n">
+      <c r="A37" s="8" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="B37" s="11" t="n"/>
-      <c r="C37" s="11" t="n"/>
-      <c r="D37" s="11" t="n"/>
-      <c r="E37" s="11" t="n"/>
-      <c r="F37" s="11" t="n"/>
-      <c r="G37" s="11" t="n"/>
-      <c r="H37" s="12" t="n"/>
+      <c r="B37" s="9" t="n"/>
+      <c r="C37" s="9" t="n"/>
+      <c r="D37" s="9" t="n"/>
+      <c r="E37" s="9" t="n"/>
+      <c r="F37" s="9" t="n"/>
+      <c r="G37" s="9" t="n"/>
+      <c r="H37" s="10" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="10" t="n"/>
-      <c r="B38" s="11" t="n"/>
-      <c r="C38" s="11" t="n"/>
-      <c r="D38" s="11" t="n"/>
-      <c r="E38" s="11" t="n"/>
-      <c r="F38" s="11" t="n"/>
-      <c r="G38" s="11" t="n"/>
-      <c r="H38" s="12" t="n"/>
+      <c r="A38" s="8" t="n"/>
+      <c r="B38" s="9" t="n"/>
+      <c r="C38" s="9" t="n"/>
+      <c r="D38" s="9" t="n"/>
+      <c r="E38" s="9" t="n"/>
+      <c r="F38" s="9" t="n"/>
+      <c r="G38" s="9" t="n"/>
+      <c r="H38" s="10" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="10" t="n">
+      <c r="A39" s="8" t="n">
         <v>0.7083333333333334</v>
       </c>
-      <c r="B39" s="11" t="n"/>
-      <c r="C39" s="11" t="n"/>
-      <c r="D39" s="11" t="n"/>
-      <c r="E39" s="11" t="n"/>
-      <c r="F39" s="11" t="n"/>
-      <c r="G39" s="11" t="n"/>
-      <c r="H39" s="12" t="n"/>
+      <c r="B39" s="9" t="n"/>
+      <c r="C39" s="9" t="n"/>
+      <c r="D39" s="9" t="n"/>
+      <c r="E39" s="9" t="n"/>
+      <c r="F39" s="9" t="n"/>
+      <c r="G39" s="9" t="n"/>
+      <c r="H39" s="10" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="10" t="n"/>
-      <c r="B40" s="11" t="n"/>
-      <c r="C40" s="11" t="n"/>
-      <c r="D40" s="11" t="n"/>
-      <c r="E40" s="11" t="n"/>
-      <c r="F40" s="11" t="n"/>
-      <c r="G40" s="11" t="n"/>
-      <c r="H40" s="12" t="n"/>
+      <c r="A40" s="8" t="n"/>
+      <c r="B40" s="9" t="n"/>
+      <c r="C40" s="9" t="n"/>
+      <c r="D40" s="9" t="n"/>
+      <c r="E40" s="9" t="n"/>
+      <c r="F40" s="9" t="n"/>
+      <c r="G40" s="9" t="n"/>
+      <c r="H40" s="10" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="10" t="n">
+      <c r="A41" s="8" t="n">
         <v>0.75</v>
       </c>
-      <c r="B41" s="11" t="n"/>
-      <c r="C41" s="11" t="n"/>
-      <c r="D41" s="11" t="n"/>
-      <c r="E41" s="11" t="n"/>
-      <c r="F41" s="11" t="n"/>
-      <c r="G41" s="11" t="n"/>
-      <c r="H41" s="12" t="n"/>
+      <c r="B41" s="9" t="n"/>
+      <c r="C41" s="9" t="n"/>
+      <c r="D41" s="9" t="n"/>
+      <c r="E41" s="9" t="n"/>
+      <c r="F41" s="9" t="n"/>
+      <c r="G41" s="9" t="n"/>
+      <c r="H41" s="10" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="10" t="n"/>
-      <c r="B42" s="11" t="n"/>
-      <c r="C42" s="11" t="n"/>
-      <c r="D42" s="11" t="n"/>
-      <c r="E42" s="11" t="n"/>
-      <c r="F42" s="11" t="n"/>
-      <c r="G42" s="11" t="n"/>
-      <c r="H42" s="12" t="n"/>
+      <c r="A42" s="8" t="n"/>
+      <c r="B42" s="9" t="n"/>
+      <c r="C42" s="9" t="n"/>
+      <c r="D42" s="9" t="n"/>
+      <c r="E42" s="9" t="n"/>
+      <c r="F42" s="9" t="n"/>
+      <c r="G42" s="9" t="n"/>
+      <c r="H42" s="10" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="10" t="n">
+      <c r="A43" s="8" t="n">
         <v>0.7916666666666666</v>
       </c>
-      <c r="B43" s="11" t="n"/>
-      <c r="C43" s="11" t="n"/>
-      <c r="D43" s="11" t="n"/>
-      <c r="E43" s="11" t="n"/>
-      <c r="F43" s="11" t="n"/>
-      <c r="G43" s="11" t="n"/>
-      <c r="H43" s="12" t="n"/>
+      <c r="B43" s="9" t="n"/>
+      <c r="C43" s="9" t="n"/>
+      <c r="D43" s="9" t="n"/>
+      <c r="E43" s="9" t="n"/>
+      <c r="F43" s="9" t="n"/>
+      <c r="G43" s="9" t="n"/>
+      <c r="H43" s="10" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="10" t="n"/>
-      <c r="B44" s="11" t="n"/>
-      <c r="C44" s="11" t="n"/>
-      <c r="D44" s="11" t="n"/>
-      <c r="E44" s="11" t="n"/>
-      <c r="F44" s="11" t="n"/>
-      <c r="G44" s="11" t="n"/>
-      <c r="H44" s="12" t="n"/>
+      <c r="A44" s="8" t="n"/>
+      <c r="B44" s="9" t="n"/>
+      <c r="C44" s="9" t="n"/>
+      <c r="D44" s="9" t="n"/>
+      <c r="E44" s="9" t="n"/>
+      <c r="F44" s="9" t="n"/>
+      <c r="G44" s="9" t="n"/>
+      <c r="H44" s="10" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="10" t="n">
+      <c r="A45" s="8" t="n">
         <v>0.8333333333333334</v>
       </c>
-      <c r="B45" s="11" t="n"/>
-      <c r="C45" s="11" t="n"/>
-      <c r="D45" s="11" t="n"/>
-      <c r="E45" s="11" t="n"/>
-      <c r="F45" s="11" t="n"/>
-      <c r="G45" s="11" t="n"/>
-      <c r="H45" s="12" t="n"/>
+      <c r="B45" s="9" t="n"/>
+      <c r="C45" s="9" t="n"/>
+      <c r="D45" s="9" t="n"/>
+      <c r="E45" s="9" t="n"/>
+      <c r="F45" s="9" t="n"/>
+      <c r="G45" s="9" t="n"/>
+      <c r="H45" s="10" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="10" t="n"/>
-      <c r="B46" s="11" t="n"/>
-      <c r="C46" s="11" t="n"/>
-      <c r="D46" s="11" t="n"/>
-      <c r="E46" s="11" t="n"/>
-      <c r="F46" s="11" t="n"/>
-      <c r="G46" s="11" t="n"/>
-      <c r="H46" s="12" t="n"/>
+      <c r="A46" s="8" t="n"/>
+      <c r="B46" s="9" t="n"/>
+      <c r="C46" s="9" t="n"/>
+      <c r="D46" s="9" t="n"/>
+      <c r="E46" s="9" t="n"/>
+      <c r="F46" s="9" t="n"/>
+      <c r="G46" s="9" t="n"/>
+      <c r="H46" s="10" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" s="10" t="n">
+      <c r="A47" s="8" t="n">
         <v>0.875</v>
       </c>
-      <c r="B47" s="11" t="n"/>
-      <c r="C47" s="11" t="n"/>
-      <c r="D47" s="11" t="n"/>
-      <c r="E47" s="11" t="n"/>
-      <c r="F47" s="11" t="n"/>
-      <c r="G47" s="11" t="n"/>
-      <c r="H47" s="12" t="n"/>
+      <c r="B47" s="9" t="n"/>
+      <c r="C47" s="9" t="n"/>
+      <c r="D47" s="9" t="n"/>
+      <c r="E47" s="9" t="n"/>
+      <c r="F47" s="9" t="n"/>
+      <c r="G47" s="9" t="n"/>
+      <c r="H47" s="10" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="10" t="n"/>
-      <c r="B48" s="11" t="n"/>
-      <c r="C48" s="11" t="n"/>
-      <c r="D48" s="11" t="n"/>
-      <c r="E48" s="11" t="n"/>
-      <c r="F48" s="11" t="n"/>
-      <c r="G48" s="11" t="n"/>
-      <c r="H48" s="12" t="n"/>
+      <c r="A48" s="8" t="n"/>
+      <c r="B48" s="9" t="n"/>
+      <c r="C48" s="9" t="n"/>
+      <c r="D48" s="9" t="n"/>
+      <c r="E48" s="9" t="n"/>
+      <c r="F48" s="9" t="n"/>
+      <c r="G48" s="9" t="n"/>
+      <c r="H48" s="10" t="n"/>
     </row>
     <row r="49">
-      <c r="A49" s="10" t="n">
+      <c r="A49" s="8" t="n">
         <v>0.9166666666666666</v>
       </c>
-      <c r="B49" s="11" t="n"/>
-      <c r="C49" s="11" t="n"/>
-      <c r="D49" s="11" t="n"/>
-      <c r="E49" s="11" t="n"/>
-      <c r="F49" s="11" t="n"/>
-      <c r="G49" s="11" t="n"/>
-      <c r="H49" s="12" t="n"/>
+      <c r="B49" s="9" t="n"/>
+      <c r="C49" s="9" t="n"/>
+      <c r="D49" s="9" t="n"/>
+      <c r="E49" s="9" t="n"/>
+      <c r="F49" s="9" t="n"/>
+      <c r="G49" s="9" t="n"/>
+      <c r="H49" s="10" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="10" t="n"/>
-      <c r="B50" s="11" t="n"/>
-      <c r="C50" s="11" t="n"/>
-      <c r="D50" s="11" t="n"/>
-      <c r="E50" s="11" t="n"/>
-      <c r="F50" s="11" t="n"/>
-      <c r="G50" s="11" t="n"/>
-      <c r="H50" s="12" t="n"/>
+      <c r="A50" s="8" t="n"/>
+      <c r="B50" s="9" t="n"/>
+      <c r="C50" s="9" t="n"/>
+      <c r="D50" s="9" t="n"/>
+      <c r="E50" s="9" t="n"/>
+      <c r="F50" s="9" t="n"/>
+      <c r="G50" s="9" t="n"/>
+      <c r="H50" s="10" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="10" t="n">
+      <c r="A51" s="8" t="n">
         <v>0.9583333333333334</v>
       </c>
-      <c r="B51" s="11" t="n"/>
-      <c r="C51" s="11" t="n"/>
-      <c r="D51" s="11" t="n"/>
-      <c r="E51" s="11" t="n"/>
-      <c r="F51" s="11" t="n"/>
-      <c r="G51" s="11" t="n"/>
-      <c r="H51" s="12" t="n"/>
+      <c r="B51" s="9" t="n"/>
+      <c r="C51" s="9" t="n"/>
+      <c r="D51" s="9" t="n"/>
+      <c r="E51" s="9" t="n"/>
+      <c r="F51" s="9" t="n"/>
+      <c r="G51" s="9" t="n"/>
+      <c r="H51" s="10" t="n"/>
     </row>
     <row r="52">
-      <c r="A52" s="13" t="n"/>
-      <c r="B52" s="14" t="n"/>
-      <c r="C52" s="14" t="n"/>
-      <c r="D52" s="14" t="n"/>
-      <c r="E52" s="14" t="n"/>
-      <c r="F52" s="14" t="n"/>
-      <c r="G52" s="14" t="n"/>
-      <c r="H52" s="15" t="n"/>
-    </row>
-    <row r="53" ht="21" customHeight="1" s="27">
+      <c r="A52" s="11" t="n"/>
+      <c r="B52" s="12" t="n"/>
+      <c r="C52" s="12" t="n"/>
+      <c r="D52" s="12" t="n"/>
+      <c r="E52" s="12" t="n"/>
+      <c r="F52" s="12" t="n"/>
+      <c r="G52" s="12" t="n"/>
+      <c r="H52" s="13" t="n"/>
+    </row>
+    <row r="53" ht="21" customHeight="1" s="25">
       <c r="A53" s="1" t="inlineStr">
         <is>
           <t>数学</t>
         </is>
       </c>
-      <c r="B53" s="5" t="n"/>
-      <c r="C53" s="5" t="n"/>
-      <c r="D53" s="5" t="n"/>
-      <c r="E53" s="5" t="n"/>
-      <c r="F53" s="5" t="n"/>
-      <c r="G53" s="5" t="n"/>
-      <c r="H53" s="6" t="n"/>
-    </row>
-    <row r="54" ht="21" customHeight="1" s="27">
+      <c r="B53" s="3" t="n"/>
+      <c r="C53" s="3" t="n"/>
+      <c r="D53" s="3" t="n"/>
+      <c r="E53" s="3" t="n"/>
+      <c r="F53" s="3" t="n"/>
+      <c r="G53" s="3" t="n"/>
+      <c r="H53" s="4" t="n"/>
+    </row>
+    <row r="54" ht="21" customHeight="1" s="25">
       <c r="A54" s="1" t="inlineStr">
         <is>
           <t>英語</t>
         </is>
       </c>
-      <c r="B54" s="16" t="n"/>
-      <c r="C54" s="16" t="n"/>
-      <c r="D54" s="16" t="n"/>
-      <c r="E54" s="16" t="n"/>
-      <c r="F54" s="16" t="n"/>
-      <c r="G54" s="16" t="n"/>
-      <c r="H54" s="17" t="n"/>
-    </row>
-    <row r="55" ht="21" customHeight="1" s="27">
-      <c r="A55" s="18" t="inlineStr">
+      <c r="B54" s="14" t="n"/>
+      <c r="C54" s="14" t="n"/>
+      <c r="D54" s="14" t="n"/>
+      <c r="E54" s="14" t="n"/>
+      <c r="F54" s="14" t="n"/>
+      <c r="G54" s="14" t="n"/>
+      <c r="H54" s="15" t="n"/>
+    </row>
+    <row r="55" ht="21" customHeight="1" s="25">
+      <c r="A55" s="16" t="inlineStr">
         <is>
           <t>国語</t>
         </is>
       </c>
-      <c r="B55" s="19" t="n"/>
-      <c r="C55" s="19" t="n"/>
-      <c r="D55" s="19" t="n"/>
-      <c r="E55" s="19" t="n"/>
-      <c r="F55" s="19" t="n"/>
-      <c r="G55" s="19" t="n"/>
-      <c r="H55" s="20" t="n"/>
-    </row>
-    <row r="56" ht="21" customHeight="1" s="27">
+      <c r="B55" s="17" t="n"/>
+      <c r="C55" s="17" t="n"/>
+      <c r="D55" s="17" t="n"/>
+      <c r="E55" s="17" t="n"/>
+      <c r="F55" s="17" t="n"/>
+      <c r="G55" s="17" t="n"/>
+      <c r="H55" s="18" t="n"/>
+    </row>
+    <row r="56" ht="21" customHeight="1" s="25">
       <c r="A56" s="1" t="inlineStr">
         <is>
           <t>理科</t>
         </is>
       </c>
-      <c r="B56" s="19" t="n"/>
-      <c r="C56" s="19" t="n"/>
-      <c r="D56" s="19" t="n"/>
-      <c r="E56" s="19" t="n"/>
-      <c r="F56" s="19" t="n"/>
-      <c r="G56" s="19" t="n"/>
-      <c r="H56" s="20" t="n"/>
-    </row>
-    <row r="57" ht="21" customHeight="1" s="27">
+      <c r="B56" s="17" t="n"/>
+      <c r="C56" s="17" t="n"/>
+      <c r="D56" s="17" t="n"/>
+      <c r="E56" s="17" t="n"/>
+      <c r="F56" s="17" t="n"/>
+      <c r="G56" s="17" t="n"/>
+      <c r="H56" s="18" t="n"/>
+    </row>
+    <row r="57" ht="21" customHeight="1" s="25">
       <c r="A57" s="1" t="inlineStr">
         <is>
           <t>社会</t>
         </is>
       </c>
-      <c r="B57" s="19" t="n"/>
-      <c r="C57" s="19" t="n"/>
-      <c r="D57" s="19" t="n"/>
-      <c r="E57" s="19" t="n"/>
-      <c r="F57" s="19" t="n"/>
-      <c r="G57" s="19" t="n"/>
-      <c r="H57" s="20" t="n"/>
-    </row>
-    <row r="58" ht="21" customHeight="1" s="27">
+      <c r="B57" s="17" t="n"/>
+      <c r="C57" s="17" t="n"/>
+      <c r="D57" s="17" t="n"/>
+      <c r="E57" s="17" t="n"/>
+      <c r="F57" s="17" t="n"/>
+      <c r="G57" s="17" t="n"/>
+      <c r="H57" s="18" t="n"/>
+    </row>
+    <row r="58" ht="21" customHeight="1" s="25">
       <c r="A58" s="1" t="inlineStr">
         <is>
           <t>隙間</t>
         </is>
       </c>
-      <c r="B58" s="19" t="n"/>
-      <c r="C58" s="19" t="n"/>
-      <c r="D58" s="19" t="n"/>
-      <c r="E58" s="19" t="n"/>
-      <c r="F58" s="19" t="n"/>
-      <c r="G58" s="19" t="n"/>
-      <c r="H58" s="20" t="n"/>
+      <c r="B58" s="17" t="n"/>
+      <c r="C58" s="17" t="n"/>
+      <c r="D58" s="17" t="n"/>
+      <c r="E58" s="17" t="n"/>
+      <c r="F58" s="17" t="n"/>
+      <c r="G58" s="17" t="n"/>
+      <c r="H58" s="18" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1456,7 +1455,7 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.35" right="0.35" top="0.35" bottom="0.35" header="0.1" footer="0.1"/>
-  <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
 
@@ -1469,699 +1468,699 @@
   <dimension ref="A1:H58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13"/>
   <cols>
-    <col width="8" customWidth="1" style="27" min="1" max="1"/>
-    <col width="12.453125" customWidth="1" style="27" min="2" max="8"/>
+    <col width="8" customWidth="1" style="25" min="1" max="1"/>
+    <col width="12.453125" customWidth="1" style="25" min="2" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="28" t="inlineStr">
+      <c r="A1" s="24" t="inlineStr">
         <is>
           <t>週間学習計画表（縦型）</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="32" customHeight="1" s="27">
-      <c r="A2" s="21" t="inlineStr">
+    <row r="2" ht="32" customHeight="1" s="25">
+      <c r="A2" s="19" t="inlineStr">
         <is>
           <t>週目標</t>
         </is>
       </c>
-      <c r="B2" s="23" t="n"/>
-      <c r="C2" s="24" t="n"/>
-      <c r="D2" s="24" t="n"/>
-      <c r="E2" s="24" t="n"/>
-      <c r="F2" s="24" t="n"/>
-      <c r="G2" s="24" t="n"/>
-      <c r="H2" s="25" t="n"/>
-    </row>
-    <row r="3" ht="18" customHeight="1" s="27">
-      <c r="A3" s="22" t="inlineStr">
+      <c r="B2" s="21" t="n"/>
+      <c r="C2" s="22" t="n"/>
+      <c r="D2" s="22" t="n"/>
+      <c r="E2" s="22" t="n"/>
+      <c r="F2" s="22" t="n"/>
+      <c r="G2" s="22" t="n"/>
+      <c r="H2" s="23" t="n"/>
+    </row>
+    <row r="3" ht="18" customHeight="1" s="25">
+      <c r="A3" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">            日付
 時間</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="26" t="inlineStr">
         <is>
           <t>月　日(月)</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="26" t="inlineStr">
         <is>
           <t>月　日(火)</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="26" t="inlineStr">
         <is>
           <t>月　日(水)</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" s="26" t="inlineStr">
         <is>
           <t>月　日(木)</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" s="26" t="inlineStr">
         <is>
           <t>月　日(金)</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="G3" s="26" t="inlineStr">
         <is>
           <t>月　日(土)</t>
         </is>
       </c>
-      <c r="H3" s="4" t="inlineStr">
+      <c r="H3" s="27" t="inlineStr">
         <is>
           <t>月　日(日)</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="16.5" customHeight="1" s="27">
+    <row r="4" ht="16.5" customHeight="1" s="25">
       <c r="A4" s="1" t="inlineStr">
         <is>
           <t>最優先</t>
         </is>
       </c>
-      <c r="B4" s="5" t="n"/>
-      <c r="C4" s="5" t="n"/>
-      <c r="D4" s="5" t="n"/>
-      <c r="E4" s="5" t="n"/>
-      <c r="F4" s="5" t="n"/>
-      <c r="G4" s="5" t="n"/>
-      <c r="H4" s="6" t="n"/>
+      <c r="B4" s="3" t="n"/>
+      <c r="C4" s="3" t="n"/>
+      <c r="D4" s="3" t="n"/>
+      <c r="E4" s="3" t="n"/>
+      <c r="F4" s="3" t="n"/>
+      <c r="G4" s="3" t="n"/>
+      <c r="H4" s="4" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="n">
+      <c r="A5" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="B5" s="8" t="n"/>
-      <c r="C5" s="8" t="n"/>
-      <c r="D5" s="8" t="n"/>
-      <c r="E5" s="8" t="n"/>
-      <c r="F5" s="8" t="n"/>
-      <c r="G5" s="8" t="n"/>
-      <c r="H5" s="9" t="n"/>
+      <c r="B5" s="6" t="n"/>
+      <c r="C5" s="6" t="n"/>
+      <c r="D5" s="6" t="n"/>
+      <c r="E5" s="6" t="n"/>
+      <c r="F5" s="6" t="n"/>
+      <c r="G5" s="6" t="n"/>
+      <c r="H5" s="7" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="n"/>
-      <c r="B6" s="11" t="n"/>
-      <c r="C6" s="11" t="n"/>
-      <c r="D6" s="11" t="n"/>
-      <c r="E6" s="11" t="n"/>
-      <c r="F6" s="11" t="n"/>
-      <c r="G6" s="11" t="n"/>
-      <c r="H6" s="12" t="n"/>
+      <c r="A6" s="8" t="n"/>
+      <c r="B6" s="9" t="n"/>
+      <c r="C6" s="9" t="n"/>
+      <c r="D6" s="9" t="n"/>
+      <c r="E6" s="9" t="n"/>
+      <c r="F6" s="9" t="n"/>
+      <c r="G6" s="9" t="n"/>
+      <c r="H6" s="10" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="10" t="n">
+      <c r="A7" s="8" t="n">
         <v>0.04166666666666666</v>
       </c>
-      <c r="B7" s="11" t="n"/>
-      <c r="C7" s="11" t="n"/>
-      <c r="D7" s="11" t="n"/>
-      <c r="E7" s="11" t="n"/>
-      <c r="F7" s="11" t="n"/>
-      <c r="G7" s="11" t="n"/>
-      <c r="H7" s="12" t="n"/>
+      <c r="B7" s="9" t="n"/>
+      <c r="C7" s="9" t="n"/>
+      <c r="D7" s="9" t="n"/>
+      <c r="E7" s="9" t="n"/>
+      <c r="F7" s="9" t="n"/>
+      <c r="G7" s="9" t="n"/>
+      <c r="H7" s="10" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="n"/>
-      <c r="B8" s="11" t="n"/>
-      <c r="C8" s="11" t="n"/>
-      <c r="D8" s="11" t="n"/>
-      <c r="E8" s="11" t="n"/>
-      <c r="F8" s="11" t="n"/>
-      <c r="G8" s="11" t="n"/>
-      <c r="H8" s="12" t="n"/>
+      <c r="A8" s="8" t="n"/>
+      <c r="B8" s="9" t="n"/>
+      <c r="C8" s="9" t="n"/>
+      <c r="D8" s="9" t="n"/>
+      <c r="E8" s="9" t="n"/>
+      <c r="F8" s="9" t="n"/>
+      <c r="G8" s="9" t="n"/>
+      <c r="H8" s="10" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="10" t="n">
+      <c r="A9" s="8" t="n">
         <v>0.08333333333333333</v>
       </c>
-      <c r="B9" s="11" t="n"/>
-      <c r="C9" s="11" t="n"/>
-      <c r="D9" s="11" t="n"/>
-      <c r="E9" s="11" t="n"/>
-      <c r="F9" s="11" t="n"/>
-      <c r="G9" s="11" t="n"/>
-      <c r="H9" s="12" t="n"/>
+      <c r="B9" s="9" t="n"/>
+      <c r="C9" s="9" t="n"/>
+      <c r="D9" s="9" t="n"/>
+      <c r="E9" s="9" t="n"/>
+      <c r="F9" s="9" t="n"/>
+      <c r="G9" s="9" t="n"/>
+      <c r="H9" s="10" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="10" t="n"/>
-      <c r="B10" s="11" t="n"/>
-      <c r="C10" s="11" t="n"/>
-      <c r="D10" s="11" t="n"/>
-      <c r="E10" s="11" t="n"/>
-      <c r="F10" s="11" t="n"/>
-      <c r="G10" s="11" t="n"/>
-      <c r="H10" s="12" t="n"/>
+      <c r="A10" s="8" t="n"/>
+      <c r="B10" s="9" t="n"/>
+      <c r="C10" s="9" t="n"/>
+      <c r="D10" s="9" t="n"/>
+      <c r="E10" s="9" t="n"/>
+      <c r="F10" s="9" t="n"/>
+      <c r="G10" s="9" t="n"/>
+      <c r="H10" s="10" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="10" t="n">
+      <c r="A11" s="8" t="n">
         <v>0.125</v>
       </c>
-      <c r="B11" s="11" t="n"/>
-      <c r="C11" s="11" t="n"/>
-      <c r="D11" s="11" t="n"/>
-      <c r="E11" s="11" t="n"/>
-      <c r="F11" s="11" t="n"/>
-      <c r="G11" s="11" t="n"/>
-      <c r="H11" s="12" t="n"/>
+      <c r="B11" s="9" t="n"/>
+      <c r="C11" s="9" t="n"/>
+      <c r="D11" s="9" t="n"/>
+      <c r="E11" s="9" t="n"/>
+      <c r="F11" s="9" t="n"/>
+      <c r="G11" s="9" t="n"/>
+      <c r="H11" s="10" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="10" t="n"/>
-      <c r="B12" s="11" t="n"/>
-      <c r="C12" s="11" t="n"/>
-      <c r="D12" s="11" t="n"/>
-      <c r="E12" s="11" t="n"/>
-      <c r="F12" s="11" t="n"/>
-      <c r="G12" s="11" t="n"/>
-      <c r="H12" s="12" t="n"/>
+      <c r="A12" s="8" t="n"/>
+      <c r="B12" s="9" t="n"/>
+      <c r="C12" s="9" t="n"/>
+      <c r="D12" s="9" t="n"/>
+      <c r="E12" s="9" t="n"/>
+      <c r="F12" s="9" t="n"/>
+      <c r="G12" s="9" t="n"/>
+      <c r="H12" s="10" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="10" t="n">
+      <c r="A13" s="8" t="n">
         <v>0.1666666666666667</v>
       </c>
-      <c r="B13" s="11" t="n"/>
-      <c r="C13" s="11" t="n"/>
-      <c r="D13" s="11" t="n"/>
-      <c r="E13" s="11" t="n"/>
-      <c r="F13" s="11" t="n"/>
-      <c r="G13" s="11" t="n"/>
-      <c r="H13" s="12" t="n"/>
+      <c r="B13" s="9" t="n"/>
+      <c r="C13" s="9" t="n"/>
+      <c r="D13" s="9" t="n"/>
+      <c r="E13" s="9" t="n"/>
+      <c r="F13" s="9" t="n"/>
+      <c r="G13" s="9" t="n"/>
+      <c r="H13" s="10" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="10" t="n"/>
-      <c r="B14" s="11" t="n"/>
-      <c r="C14" s="11" t="n"/>
-      <c r="D14" s="11" t="n"/>
-      <c r="E14" s="11" t="n"/>
-      <c r="F14" s="11" t="n"/>
-      <c r="G14" s="11" t="n"/>
-      <c r="H14" s="12" t="n"/>
+      <c r="A14" s="8" t="n"/>
+      <c r="B14" s="9" t="n"/>
+      <c r="C14" s="9" t="n"/>
+      <c r="D14" s="9" t="n"/>
+      <c r="E14" s="9" t="n"/>
+      <c r="F14" s="9" t="n"/>
+      <c r="G14" s="9" t="n"/>
+      <c r="H14" s="10" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="10" t="n">
+      <c r="A15" s="8" t="n">
         <v>0.2083333333333333</v>
       </c>
-      <c r="B15" s="11" t="n"/>
-      <c r="C15" s="11" t="n"/>
-      <c r="D15" s="11" t="n"/>
-      <c r="E15" s="11" t="n"/>
-      <c r="F15" s="11" t="n"/>
-      <c r="G15" s="11" t="n"/>
-      <c r="H15" s="12" t="n"/>
+      <c r="B15" s="9" t="n"/>
+      <c r="C15" s="9" t="n"/>
+      <c r="D15" s="9" t="n"/>
+      <c r="E15" s="9" t="n"/>
+      <c r="F15" s="9" t="n"/>
+      <c r="G15" s="9" t="n"/>
+      <c r="H15" s="10" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="10" t="n"/>
-      <c r="B16" s="11" t="n"/>
-      <c r="C16" s="11" t="n"/>
-      <c r="D16" s="11" t="n"/>
-      <c r="E16" s="11" t="n"/>
-      <c r="F16" s="11" t="n"/>
-      <c r="G16" s="11" t="n"/>
-      <c r="H16" s="12" t="n"/>
+      <c r="A16" s="8" t="n"/>
+      <c r="B16" s="9" t="n"/>
+      <c r="C16" s="9" t="n"/>
+      <c r="D16" s="9" t="n"/>
+      <c r="E16" s="9" t="n"/>
+      <c r="F16" s="9" t="n"/>
+      <c r="G16" s="9" t="n"/>
+      <c r="H16" s="10" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="10" t="n">
+      <c r="A17" s="8" t="n">
         <v>0.25</v>
       </c>
-      <c r="B17" s="11" t="n"/>
-      <c r="C17" s="11" t="n"/>
-      <c r="D17" s="11" t="n"/>
-      <c r="E17" s="11" t="n"/>
-      <c r="F17" s="11" t="n"/>
-      <c r="G17" s="11" t="n"/>
-      <c r="H17" s="12" t="n"/>
+      <c r="B17" s="9" t="n"/>
+      <c r="C17" s="9" t="n"/>
+      <c r="D17" s="9" t="n"/>
+      <c r="E17" s="9" t="n"/>
+      <c r="F17" s="9" t="n"/>
+      <c r="G17" s="9" t="n"/>
+      <c r="H17" s="10" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="10" t="n"/>
-      <c r="B18" s="11" t="n"/>
-      <c r="C18" s="11" t="n"/>
-      <c r="D18" s="11" t="n"/>
-      <c r="E18" s="11" t="n"/>
-      <c r="F18" s="11" t="n"/>
-      <c r="G18" s="11" t="n"/>
-      <c r="H18" s="12" t="n"/>
+      <c r="A18" s="8" t="n"/>
+      <c r="B18" s="9" t="n"/>
+      <c r="C18" s="9" t="n"/>
+      <c r="D18" s="9" t="n"/>
+      <c r="E18" s="9" t="n"/>
+      <c r="F18" s="9" t="n"/>
+      <c r="G18" s="9" t="n"/>
+      <c r="H18" s="10" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="10" t="n">
+      <c r="A19" s="8" t="n">
         <v>0.2916666666666667</v>
       </c>
-      <c r="B19" s="11" t="n"/>
-      <c r="C19" s="11" t="n"/>
-      <c r="D19" s="11" t="n"/>
-      <c r="E19" s="11" t="n"/>
-      <c r="F19" s="11" t="n"/>
-      <c r="G19" s="11" t="n"/>
-      <c r="H19" s="12" t="n"/>
+      <c r="B19" s="9" t="n"/>
+      <c r="C19" s="9" t="n"/>
+      <c r="D19" s="9" t="n"/>
+      <c r="E19" s="9" t="n"/>
+      <c r="F19" s="9" t="n"/>
+      <c r="G19" s="9" t="n"/>
+      <c r="H19" s="10" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="10" t="n"/>
-      <c r="B20" s="11" t="n"/>
-      <c r="C20" s="11" t="n"/>
-      <c r="D20" s="11" t="n"/>
-      <c r="E20" s="11" t="n"/>
-      <c r="F20" s="11" t="n"/>
-      <c r="G20" s="11" t="n"/>
-      <c r="H20" s="12" t="n"/>
+      <c r="A20" s="8" t="n"/>
+      <c r="B20" s="9" t="n"/>
+      <c r="C20" s="9" t="n"/>
+      <c r="D20" s="9" t="n"/>
+      <c r="E20" s="9" t="n"/>
+      <c r="F20" s="9" t="n"/>
+      <c r="G20" s="9" t="n"/>
+      <c r="H20" s="10" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="10" t="n">
+      <c r="A21" s="8" t="n">
         <v>0.3333333333333333</v>
       </c>
-      <c r="B21" s="11" t="n"/>
-      <c r="C21" s="11" t="n"/>
-      <c r="D21" s="11" t="n"/>
-      <c r="E21" s="11" t="n"/>
-      <c r="F21" s="11" t="n"/>
-      <c r="G21" s="11" t="n"/>
-      <c r="H21" s="12" t="n"/>
+      <c r="B21" s="9" t="n"/>
+      <c r="C21" s="9" t="n"/>
+      <c r="D21" s="9" t="n"/>
+      <c r="E21" s="9" t="n"/>
+      <c r="F21" s="9" t="n"/>
+      <c r="G21" s="9" t="n"/>
+      <c r="H21" s="10" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="10" t="n"/>
-      <c r="B22" s="11" t="n"/>
-      <c r="C22" s="11" t="n"/>
-      <c r="D22" s="11" t="n"/>
-      <c r="E22" s="11" t="n"/>
-      <c r="F22" s="11" t="n"/>
-      <c r="G22" s="11" t="n"/>
-      <c r="H22" s="12" t="n"/>
+      <c r="A22" s="8" t="n"/>
+      <c r="B22" s="9" t="n"/>
+      <c r="C22" s="9" t="n"/>
+      <c r="D22" s="9" t="n"/>
+      <c r="E22" s="9" t="n"/>
+      <c r="F22" s="9" t="n"/>
+      <c r="G22" s="9" t="n"/>
+      <c r="H22" s="10" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="10" t="n">
+      <c r="A23" s="8" t="n">
         <v>0.375</v>
       </c>
-      <c r="B23" s="11" t="n"/>
-      <c r="C23" s="11" t="n"/>
-      <c r="D23" s="11" t="n"/>
-      <c r="E23" s="11" t="n"/>
-      <c r="F23" s="11" t="n"/>
-      <c r="G23" s="11" t="n"/>
-      <c r="H23" s="12" t="n"/>
+      <c r="B23" s="9" t="n"/>
+      <c r="C23" s="9" t="n"/>
+      <c r="D23" s="9" t="n"/>
+      <c r="E23" s="9" t="n"/>
+      <c r="F23" s="9" t="n"/>
+      <c r="G23" s="9" t="n"/>
+      <c r="H23" s="10" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="10" t="n"/>
-      <c r="B24" s="11" t="n"/>
-      <c r="C24" s="11" t="n"/>
-      <c r="D24" s="11" t="n"/>
-      <c r="E24" s="11" t="n"/>
-      <c r="F24" s="11" t="n"/>
-      <c r="G24" s="11" t="n"/>
-      <c r="H24" s="12" t="n"/>
+      <c r="A24" s="8" t="n"/>
+      <c r="B24" s="9" t="n"/>
+      <c r="C24" s="9" t="n"/>
+      <c r="D24" s="9" t="n"/>
+      <c r="E24" s="9" t="n"/>
+      <c r="F24" s="9" t="n"/>
+      <c r="G24" s="9" t="n"/>
+      <c r="H24" s="10" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="10" t="n">
+      <c r="A25" s="8" t="n">
         <v>0.4166666666666667</v>
       </c>
-      <c r="B25" s="11" t="n"/>
-      <c r="C25" s="11" t="n"/>
-      <c r="D25" s="11" t="n"/>
-      <c r="E25" s="11" t="n"/>
-      <c r="F25" s="11" t="n"/>
-      <c r="G25" s="11" t="n"/>
-      <c r="H25" s="12" t="n"/>
+      <c r="B25" s="9" t="n"/>
+      <c r="C25" s="9" t="n"/>
+      <c r="D25" s="9" t="n"/>
+      <c r="E25" s="9" t="n"/>
+      <c r="F25" s="9" t="n"/>
+      <c r="G25" s="9" t="n"/>
+      <c r="H25" s="10" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="10" t="n"/>
-      <c r="B26" s="11" t="n"/>
-      <c r="C26" s="11" t="n"/>
-      <c r="D26" s="11" t="n"/>
-      <c r="E26" s="11" t="n"/>
-      <c r="F26" s="11" t="n"/>
-      <c r="G26" s="11" t="n"/>
-      <c r="H26" s="12" t="n"/>
+      <c r="A26" s="8" t="n"/>
+      <c r="B26" s="9" t="n"/>
+      <c r="C26" s="9" t="n"/>
+      <c r="D26" s="9" t="n"/>
+      <c r="E26" s="9" t="n"/>
+      <c r="F26" s="9" t="n"/>
+      <c r="G26" s="9" t="n"/>
+      <c r="H26" s="10" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="10" t="n">
+      <c r="A27" s="8" t="n">
         <v>0.4583333333333333</v>
       </c>
-      <c r="B27" s="11" t="n"/>
-      <c r="C27" s="11" t="n"/>
-      <c r="D27" s="11" t="n"/>
-      <c r="E27" s="11" t="n"/>
-      <c r="F27" s="11" t="n"/>
-      <c r="G27" s="11" t="n"/>
-      <c r="H27" s="12" t="n"/>
+      <c r="B27" s="9" t="n"/>
+      <c r="C27" s="9" t="n"/>
+      <c r="D27" s="9" t="n"/>
+      <c r="E27" s="9" t="n"/>
+      <c r="F27" s="9" t="n"/>
+      <c r="G27" s="9" t="n"/>
+      <c r="H27" s="10" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="10" t="n"/>
-      <c r="B28" s="11" t="n"/>
-      <c r="C28" s="11" t="n"/>
-      <c r="D28" s="11" t="n"/>
-      <c r="E28" s="11" t="n"/>
-      <c r="F28" s="11" t="n"/>
-      <c r="G28" s="11" t="n"/>
-      <c r="H28" s="12" t="n"/>
+      <c r="A28" s="8" t="n"/>
+      <c r="B28" s="9" t="n"/>
+      <c r="C28" s="9" t="n"/>
+      <c r="D28" s="9" t="n"/>
+      <c r="E28" s="9" t="n"/>
+      <c r="F28" s="9" t="n"/>
+      <c r="G28" s="9" t="n"/>
+      <c r="H28" s="10" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="10" t="n">
+      <c r="A29" s="8" t="n">
         <v>0.5</v>
       </c>
-      <c r="B29" s="11" t="n"/>
-      <c r="C29" s="11" t="n"/>
-      <c r="D29" s="11" t="n"/>
-      <c r="E29" s="11" t="n"/>
-      <c r="F29" s="11" t="n"/>
-      <c r="G29" s="11" t="n"/>
-      <c r="H29" s="12" t="n"/>
+      <c r="B29" s="9" t="n"/>
+      <c r="C29" s="9" t="n"/>
+      <c r="D29" s="9" t="n"/>
+      <c r="E29" s="9" t="n"/>
+      <c r="F29" s="9" t="n"/>
+      <c r="G29" s="9" t="n"/>
+      <c r="H29" s="10" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="10" t="n"/>
-      <c r="B30" s="11" t="n"/>
-      <c r="C30" s="11" t="n"/>
-      <c r="D30" s="11" t="n"/>
-      <c r="E30" s="11" t="n"/>
-      <c r="F30" s="11" t="n"/>
-      <c r="G30" s="11" t="n"/>
-      <c r="H30" s="12" t="n"/>
+      <c r="A30" s="8" t="n"/>
+      <c r="B30" s="9" t="n"/>
+      <c r="C30" s="9" t="n"/>
+      <c r="D30" s="9" t="n"/>
+      <c r="E30" s="9" t="n"/>
+      <c r="F30" s="9" t="n"/>
+      <c r="G30" s="9" t="n"/>
+      <c r="H30" s="10" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="10" t="n">
+      <c r="A31" s="8" t="n">
         <v>0.5416666666666666</v>
       </c>
-      <c r="B31" s="11" t="n"/>
-      <c r="C31" s="11" t="n"/>
-      <c r="D31" s="11" t="n"/>
-      <c r="E31" s="11" t="n"/>
-      <c r="F31" s="11" t="n"/>
-      <c r="G31" s="11" t="n"/>
-      <c r="H31" s="12" t="n"/>
+      <c r="B31" s="9" t="n"/>
+      <c r="C31" s="9" t="n"/>
+      <c r="D31" s="9" t="n"/>
+      <c r="E31" s="9" t="n"/>
+      <c r="F31" s="9" t="n"/>
+      <c r="G31" s="9" t="n"/>
+      <c r="H31" s="10" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="10" t="n"/>
-      <c r="B32" s="11" t="n"/>
-      <c r="C32" s="11" t="n"/>
-      <c r="D32" s="11" t="n"/>
-      <c r="E32" s="11" t="n"/>
-      <c r="F32" s="11" t="n"/>
-      <c r="G32" s="11" t="n"/>
-      <c r="H32" s="12" t="n"/>
+      <c r="A32" s="8" t="n"/>
+      <c r="B32" s="9" t="n"/>
+      <c r="C32" s="9" t="n"/>
+      <c r="D32" s="9" t="n"/>
+      <c r="E32" s="9" t="n"/>
+      <c r="F32" s="9" t="n"/>
+      <c r="G32" s="9" t="n"/>
+      <c r="H32" s="10" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="10" t="n">
+      <c r="A33" s="8" t="n">
         <v>0.5833333333333334</v>
       </c>
-      <c r="B33" s="11" t="n"/>
-      <c r="C33" s="11" t="n"/>
-      <c r="D33" s="11" t="n"/>
-      <c r="E33" s="11" t="n"/>
-      <c r="F33" s="11" t="n"/>
-      <c r="G33" s="11" t="n"/>
-      <c r="H33" s="12" t="n"/>
+      <c r="B33" s="9" t="n"/>
+      <c r="C33" s="9" t="n"/>
+      <c r="D33" s="9" t="n"/>
+      <c r="E33" s="9" t="n"/>
+      <c r="F33" s="9" t="n"/>
+      <c r="G33" s="9" t="n"/>
+      <c r="H33" s="10" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="10" t="n"/>
-      <c r="B34" s="11" t="n"/>
-      <c r="C34" s="11" t="n"/>
-      <c r="D34" s="11" t="n"/>
-      <c r="E34" s="11" t="n"/>
-      <c r="F34" s="11" t="n"/>
-      <c r="G34" s="11" t="n"/>
-      <c r="H34" s="12" t="n"/>
+      <c r="A34" s="8" t="n"/>
+      <c r="B34" s="9" t="n"/>
+      <c r="C34" s="9" t="n"/>
+      <c r="D34" s="9" t="n"/>
+      <c r="E34" s="9" t="n"/>
+      <c r="F34" s="9" t="n"/>
+      <c r="G34" s="9" t="n"/>
+      <c r="H34" s="10" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="10" t="n">
+      <c r="A35" s="8" t="n">
         <v>0.625</v>
       </c>
-      <c r="B35" s="11" t="n"/>
-      <c r="C35" s="11" t="n"/>
-      <c r="D35" s="11" t="n"/>
-      <c r="E35" s="11" t="n"/>
-      <c r="F35" s="11" t="n"/>
-      <c r="G35" s="11" t="n"/>
-      <c r="H35" s="12" t="n"/>
+      <c r="B35" s="9" t="n"/>
+      <c r="C35" s="9" t="n"/>
+      <c r="D35" s="9" t="n"/>
+      <c r="E35" s="9" t="n"/>
+      <c r="F35" s="9" t="n"/>
+      <c r="G35" s="9" t="n"/>
+      <c r="H35" s="10" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="10" t="n"/>
-      <c r="B36" s="11" t="n"/>
-      <c r="C36" s="11" t="n"/>
-      <c r="D36" s="11" t="n"/>
-      <c r="E36" s="11" t="n"/>
-      <c r="F36" s="11" t="n"/>
-      <c r="G36" s="11" t="n"/>
-      <c r="H36" s="12" t="n"/>
+      <c r="A36" s="8" t="n"/>
+      <c r="B36" s="9" t="n"/>
+      <c r="C36" s="9" t="n"/>
+      <c r="D36" s="9" t="n"/>
+      <c r="E36" s="9" t="n"/>
+      <c r="F36" s="9" t="n"/>
+      <c r="G36" s="9" t="n"/>
+      <c r="H36" s="10" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="10" t="n">
+      <c r="A37" s="8" t="n">
         <v>0.6666666666666666</v>
       </c>
-      <c r="B37" s="11" t="n"/>
-      <c r="C37" s="11" t="n"/>
-      <c r="D37" s="11" t="n"/>
-      <c r="E37" s="11" t="n"/>
-      <c r="F37" s="11" t="n"/>
-      <c r="G37" s="11" t="n"/>
-      <c r="H37" s="12" t="n"/>
+      <c r="B37" s="9" t="n"/>
+      <c r="C37" s="9" t="n"/>
+      <c r="D37" s="9" t="n"/>
+      <c r="E37" s="9" t="n"/>
+      <c r="F37" s="9" t="n"/>
+      <c r="G37" s="9" t="n"/>
+      <c r="H37" s="10" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="10" t="n"/>
-      <c r="B38" s="11" t="n"/>
-      <c r="C38" s="11" t="n"/>
-      <c r="D38" s="11" t="n"/>
-      <c r="E38" s="11" t="n"/>
-      <c r="F38" s="11" t="n"/>
-      <c r="G38" s="11" t="n"/>
-      <c r="H38" s="12" t="n"/>
+      <c r="A38" s="8" t="n"/>
+      <c r="B38" s="9" t="n"/>
+      <c r="C38" s="9" t="n"/>
+      <c r="D38" s="9" t="n"/>
+      <c r="E38" s="9" t="n"/>
+      <c r="F38" s="9" t="n"/>
+      <c r="G38" s="9" t="n"/>
+      <c r="H38" s="10" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="10" t="n">
+      <c r="A39" s="8" t="n">
         <v>0.7083333333333334</v>
       </c>
-      <c r="B39" s="11" t="n"/>
-      <c r="C39" s="11" t="n"/>
-      <c r="D39" s="11" t="n"/>
-      <c r="E39" s="11" t="n"/>
-      <c r="F39" s="11" t="n"/>
-      <c r="G39" s="11" t="n"/>
-      <c r="H39" s="12" t="n"/>
+      <c r="B39" s="9" t="n"/>
+      <c r="C39" s="9" t="n"/>
+      <c r="D39" s="9" t="n"/>
+      <c r="E39" s="9" t="n"/>
+      <c r="F39" s="9" t="n"/>
+      <c r="G39" s="9" t="n"/>
+      <c r="H39" s="10" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="10" t="n"/>
-      <c r="B40" s="11" t="n"/>
-      <c r="C40" s="11" t="n"/>
-      <c r="D40" s="11" t="n"/>
-      <c r="E40" s="11" t="n"/>
-      <c r="F40" s="11" t="n"/>
-      <c r="G40" s="11" t="n"/>
-      <c r="H40" s="12" t="n"/>
+      <c r="A40" s="8" t="n"/>
+      <c r="B40" s="9" t="n"/>
+      <c r="C40" s="9" t="n"/>
+      <c r="D40" s="9" t="n"/>
+      <c r="E40" s="9" t="n"/>
+      <c r="F40" s="9" t="n"/>
+      <c r="G40" s="9" t="n"/>
+      <c r="H40" s="10" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="10" t="n">
+      <c r="A41" s="8" t="n">
         <v>0.75</v>
       </c>
-      <c r="B41" s="11" t="n"/>
-      <c r="C41" s="11" t="n"/>
-      <c r="D41" s="11" t="n"/>
-      <c r="E41" s="11" t="n"/>
-      <c r="F41" s="11" t="n"/>
-      <c r="G41" s="11" t="n"/>
-      <c r="H41" s="12" t="n"/>
+      <c r="B41" s="9" t="n"/>
+      <c r="C41" s="9" t="n"/>
+      <c r="D41" s="9" t="n"/>
+      <c r="E41" s="9" t="n"/>
+      <c r="F41" s="9" t="n"/>
+      <c r="G41" s="9" t="n"/>
+      <c r="H41" s="10" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="10" t="n"/>
-      <c r="B42" s="11" t="n"/>
-      <c r="C42" s="11" t="n"/>
-      <c r="D42" s="11" t="n"/>
-      <c r="E42" s="11" t="n"/>
-      <c r="F42" s="11" t="n"/>
-      <c r="G42" s="11" t="n"/>
-      <c r="H42" s="12" t="n"/>
+      <c r="A42" s="8" t="n"/>
+      <c r="B42" s="9" t="n"/>
+      <c r="C42" s="9" t="n"/>
+      <c r="D42" s="9" t="n"/>
+      <c r="E42" s="9" t="n"/>
+      <c r="F42" s="9" t="n"/>
+      <c r="G42" s="9" t="n"/>
+      <c r="H42" s="10" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="10" t="n">
+      <c r="A43" s="8" t="n">
         <v>0.7916666666666666</v>
       </c>
-      <c r="B43" s="11" t="n"/>
-      <c r="C43" s="11" t="n"/>
-      <c r="D43" s="11" t="n"/>
-      <c r="E43" s="11" t="n"/>
-      <c r="F43" s="11" t="n"/>
-      <c r="G43" s="11" t="n"/>
-      <c r="H43" s="12" t="n"/>
+      <c r="B43" s="9" t="n"/>
+      <c r="C43" s="9" t="n"/>
+      <c r="D43" s="9" t="n"/>
+      <c r="E43" s="9" t="n"/>
+      <c r="F43" s="9" t="n"/>
+      <c r="G43" s="9" t="n"/>
+      <c r="H43" s="10" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="10" t="n"/>
-      <c r="B44" s="11" t="n"/>
-      <c r="C44" s="11" t="n"/>
-      <c r="D44" s="11" t="n"/>
-      <c r="E44" s="11" t="n"/>
-      <c r="F44" s="11" t="n"/>
-      <c r="G44" s="11" t="n"/>
-      <c r="H44" s="12" t="n"/>
+      <c r="A44" s="8" t="n"/>
+      <c r="B44" s="9" t="n"/>
+      <c r="C44" s="9" t="n"/>
+      <c r="D44" s="9" t="n"/>
+      <c r="E44" s="9" t="n"/>
+      <c r="F44" s="9" t="n"/>
+      <c r="G44" s="9" t="n"/>
+      <c r="H44" s="10" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="10" t="n">
+      <c r="A45" s="8" t="n">
         <v>0.8333333333333334</v>
       </c>
-      <c r="B45" s="11" t="n"/>
-      <c r="C45" s="11" t="n"/>
-      <c r="D45" s="11" t="n"/>
-      <c r="E45" s="11" t="n"/>
-      <c r="F45" s="11" t="n"/>
-      <c r="G45" s="11" t="n"/>
-      <c r="H45" s="12" t="n"/>
+      <c r="B45" s="9" t="n"/>
+      <c r="C45" s="9" t="n"/>
+      <c r="D45" s="9" t="n"/>
+      <c r="E45" s="9" t="n"/>
+      <c r="F45" s="9" t="n"/>
+      <c r="G45" s="9" t="n"/>
+      <c r="H45" s="10" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="10" t="n"/>
-      <c r="B46" s="11" t="n"/>
-      <c r="C46" s="11" t="n"/>
-      <c r="D46" s="11" t="n"/>
-      <c r="E46" s="11" t="n"/>
-      <c r="F46" s="11" t="n"/>
-      <c r="G46" s="11" t="n"/>
-      <c r="H46" s="12" t="n"/>
+      <c r="A46" s="8" t="n"/>
+      <c r="B46" s="9" t="n"/>
+      <c r="C46" s="9" t="n"/>
+      <c r="D46" s="9" t="n"/>
+      <c r="E46" s="9" t="n"/>
+      <c r="F46" s="9" t="n"/>
+      <c r="G46" s="9" t="n"/>
+      <c r="H46" s="10" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" s="10" t="n">
+      <c r="A47" s="8" t="n">
         <v>0.875</v>
       </c>
-      <c r="B47" s="11" t="n"/>
-      <c r="C47" s="11" t="n"/>
-      <c r="D47" s="11" t="n"/>
-      <c r="E47" s="11" t="n"/>
-      <c r="F47" s="11" t="n"/>
-      <c r="G47" s="11" t="n"/>
-      <c r="H47" s="12" t="n"/>
+      <c r="B47" s="9" t="n"/>
+      <c r="C47" s="9" t="n"/>
+      <c r="D47" s="9" t="n"/>
+      <c r="E47" s="9" t="n"/>
+      <c r="F47" s="9" t="n"/>
+      <c r="G47" s="9" t="n"/>
+      <c r="H47" s="10" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="10" t="n"/>
-      <c r="B48" s="11" t="n"/>
-      <c r="C48" s="11" t="n"/>
-      <c r="D48" s="11" t="n"/>
-      <c r="E48" s="11" t="n"/>
-      <c r="F48" s="11" t="n"/>
-      <c r="G48" s="11" t="n"/>
-      <c r="H48" s="12" t="n"/>
+      <c r="A48" s="8" t="n"/>
+      <c r="B48" s="9" t="n"/>
+      <c r="C48" s="9" t="n"/>
+      <c r="D48" s="9" t="n"/>
+      <c r="E48" s="9" t="n"/>
+      <c r="F48" s="9" t="n"/>
+      <c r="G48" s="9" t="n"/>
+      <c r="H48" s="10" t="n"/>
     </row>
     <row r="49">
-      <c r="A49" s="10" t="n">
+      <c r="A49" s="8" t="n">
         <v>0.9166666666666666</v>
       </c>
-      <c r="B49" s="11" t="n"/>
-      <c r="C49" s="11" t="n"/>
-      <c r="D49" s="11" t="n"/>
-      <c r="E49" s="11" t="n"/>
-      <c r="F49" s="11" t="n"/>
-      <c r="G49" s="11" t="n"/>
-      <c r="H49" s="12" t="n"/>
+      <c r="B49" s="9" t="n"/>
+      <c r="C49" s="9" t="n"/>
+      <c r="D49" s="9" t="n"/>
+      <c r="E49" s="9" t="n"/>
+      <c r="F49" s="9" t="n"/>
+      <c r="G49" s="9" t="n"/>
+      <c r="H49" s="10" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="10" t="n"/>
-      <c r="B50" s="11" t="n"/>
-      <c r="C50" s="11" t="n"/>
-      <c r="D50" s="11" t="n"/>
-      <c r="E50" s="11" t="n"/>
-      <c r="F50" s="11" t="n"/>
-      <c r="G50" s="11" t="n"/>
-      <c r="H50" s="12" t="n"/>
+      <c r="A50" s="8" t="n"/>
+      <c r="B50" s="9" t="n"/>
+      <c r="C50" s="9" t="n"/>
+      <c r="D50" s="9" t="n"/>
+      <c r="E50" s="9" t="n"/>
+      <c r="F50" s="9" t="n"/>
+      <c r="G50" s="9" t="n"/>
+      <c r="H50" s="10" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="10" t="n">
+      <c r="A51" s="8" t="n">
         <v>0.9583333333333334</v>
       </c>
-      <c r="B51" s="11" t="n"/>
-      <c r="C51" s="11" t="n"/>
-      <c r="D51" s="11" t="n"/>
-      <c r="E51" s="11" t="n"/>
-      <c r="F51" s="11" t="n"/>
-      <c r="G51" s="11" t="n"/>
-      <c r="H51" s="12" t="n"/>
+      <c r="B51" s="9" t="n"/>
+      <c r="C51" s="9" t="n"/>
+      <c r="D51" s="9" t="n"/>
+      <c r="E51" s="9" t="n"/>
+      <c r="F51" s="9" t="n"/>
+      <c r="G51" s="9" t="n"/>
+      <c r="H51" s="10" t="n"/>
     </row>
     <row r="52">
-      <c r="A52" s="13" t="n"/>
-      <c r="B52" s="14" t="n"/>
-      <c r="C52" s="14" t="n"/>
-      <c r="D52" s="14" t="n"/>
-      <c r="E52" s="14" t="n"/>
-      <c r="F52" s="14" t="n"/>
-      <c r="G52" s="14" t="n"/>
-      <c r="H52" s="15" t="n"/>
-    </row>
-    <row r="53" ht="21" customHeight="1" s="27">
+      <c r="A52" s="11" t="n"/>
+      <c r="B52" s="12" t="n"/>
+      <c r="C52" s="12" t="n"/>
+      <c r="D52" s="12" t="n"/>
+      <c r="E52" s="12" t="n"/>
+      <c r="F52" s="12" t="n"/>
+      <c r="G52" s="12" t="n"/>
+      <c r="H52" s="13" t="n"/>
+    </row>
+    <row r="53" ht="21" customHeight="1" s="25">
       <c r="A53" s="1" t="inlineStr">
         <is>
           <t>数学</t>
         </is>
       </c>
-      <c r="B53" s="5" t="n"/>
-      <c r="C53" s="5" t="n"/>
-      <c r="D53" s="5" t="n"/>
-      <c r="E53" s="5" t="n"/>
-      <c r="F53" s="5" t="n"/>
-      <c r="G53" s="5" t="n"/>
-      <c r="H53" s="6" t="n"/>
-    </row>
-    <row r="54" ht="21" customHeight="1" s="27">
+      <c r="B53" s="3" t="n"/>
+      <c r="C53" s="3" t="n"/>
+      <c r="D53" s="3" t="n"/>
+      <c r="E53" s="3" t="n"/>
+      <c r="F53" s="3" t="n"/>
+      <c r="G53" s="3" t="n"/>
+      <c r="H53" s="4" t="n"/>
+    </row>
+    <row r="54" ht="21" customHeight="1" s="25">
       <c r="A54" s="1" t="inlineStr">
         <is>
           <t>英語</t>
         </is>
       </c>
-      <c r="B54" s="16" t="n"/>
-      <c r="C54" s="16" t="n"/>
-      <c r="D54" s="16" t="n"/>
-      <c r="E54" s="16" t="n"/>
-      <c r="F54" s="16" t="n"/>
-      <c r="G54" s="16" t="n"/>
-      <c r="H54" s="17" t="n"/>
-    </row>
-    <row r="55" ht="21" customHeight="1" s="27">
-      <c r="A55" s="18" t="inlineStr">
+      <c r="B54" s="14" t="n"/>
+      <c r="C54" s="14" t="n"/>
+      <c r="D54" s="14" t="n"/>
+      <c r="E54" s="14" t="n"/>
+      <c r="F54" s="14" t="n"/>
+      <c r="G54" s="14" t="n"/>
+      <c r="H54" s="15" t="n"/>
+    </row>
+    <row r="55" ht="21" customHeight="1" s="25">
+      <c r="A55" s="16" t="inlineStr">
         <is>
           <t>国語</t>
         </is>
       </c>
-      <c r="B55" s="19" t="n"/>
-      <c r="C55" s="19" t="n"/>
-      <c r="D55" s="19" t="n"/>
-      <c r="E55" s="19" t="n"/>
-      <c r="F55" s="19" t="n"/>
-      <c r="G55" s="19" t="n"/>
-      <c r="H55" s="20" t="n"/>
-    </row>
-    <row r="56" ht="21" customHeight="1" s="27">
+      <c r="B55" s="17" t="n"/>
+      <c r="C55" s="17" t="n"/>
+      <c r="D55" s="17" t="n"/>
+      <c r="E55" s="17" t="n"/>
+      <c r="F55" s="17" t="n"/>
+      <c r="G55" s="17" t="n"/>
+      <c r="H55" s="18" t="n"/>
+    </row>
+    <row r="56" ht="21" customHeight="1" s="25">
       <c r="A56" s="1" t="inlineStr">
         <is>
           <t>理科</t>
         </is>
       </c>
-      <c r="B56" s="19" t="n"/>
-      <c r="C56" s="19" t="n"/>
-      <c r="D56" s="19" t="n"/>
-      <c r="E56" s="19" t="n"/>
-      <c r="F56" s="19" t="n"/>
-      <c r="G56" s="19" t="n"/>
-      <c r="H56" s="20" t="n"/>
-    </row>
-    <row r="57" ht="21" customHeight="1" s="27">
+      <c r="B56" s="17" t="n"/>
+      <c r="C56" s="17" t="n"/>
+      <c r="D56" s="17" t="n"/>
+      <c r="E56" s="17" t="n"/>
+      <c r="F56" s="17" t="n"/>
+      <c r="G56" s="17" t="n"/>
+      <c r="H56" s="18" t="n"/>
+    </row>
+    <row r="57" ht="21" customHeight="1" s="25">
       <c r="A57" s="1" t="inlineStr">
         <is>
           <t>社会</t>
         </is>
       </c>
-      <c r="B57" s="19" t="n"/>
-      <c r="C57" s="19" t="n"/>
-      <c r="D57" s="19" t="n"/>
-      <c r="E57" s="19" t="n"/>
-      <c r="F57" s="19" t="n"/>
-      <c r="G57" s="19" t="n"/>
-      <c r="H57" s="20" t="n"/>
-    </row>
-    <row r="58" ht="21" customHeight="1" s="27">
+      <c r="B57" s="17" t="n"/>
+      <c r="C57" s="17" t="n"/>
+      <c r="D57" s="17" t="n"/>
+      <c r="E57" s="17" t="n"/>
+      <c r="F57" s="17" t="n"/>
+      <c r="G57" s="17" t="n"/>
+      <c r="H57" s="18" t="n"/>
+    </row>
+    <row r="58" ht="21" customHeight="1" s="25">
       <c r="A58" s="1" t="inlineStr">
         <is>
           <t>隙間</t>
         </is>
       </c>
-      <c r="B58" s="19" t="n"/>
-      <c r="C58" s="19" t="n"/>
-      <c r="D58" s="19" t="n"/>
-      <c r="E58" s="19" t="n"/>
-      <c r="F58" s="19" t="n"/>
-      <c r="G58" s="19" t="n"/>
-      <c r="H58" s="20" t="n"/>
+      <c r="B58" s="17" t="n"/>
+      <c r="C58" s="17" t="n"/>
+      <c r="D58" s="17" t="n"/>
+      <c r="E58" s="17" t="n"/>
+      <c r="F58" s="17" t="n"/>
+      <c r="G58" s="17" t="n"/>
+      <c r="H58" s="18" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2170,6 +2169,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.35" right="0.35" top="0.35" bottom="0.35" header="0.1" footer="0.1"/>
-  <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>